--- a/src/main/kotlin/com/kcvn/spm/assets/template/ExportPlanTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ExportPlanTemplate.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Thông tin kế hoạch" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -19,23 +19,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>Lớp</t>
-  </si>
-  <si>
-    <t>Mã công đoạn</t>
-  </si>
-  <si>
-    <t>Tên công đoạn</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Tỷ lệ đạt</t>
   </si>
   <si>
-    <t>Mã</t>
-  </si>
-  <si>
     <t>Tồn</t>
   </si>
   <si>
@@ -43,6 +31,30 @@
   </si>
   <si>
     <t>日程</t>
+  </si>
+  <si>
+    <t>Tên sản phẩm</t>
+  </si>
+  <si>
+    <t>Pcs/SH</t>
+  </si>
+  <si>
+    <t>Block/SH</t>
+  </si>
+  <si>
+    <t>Line</t>
+  </si>
+  <si>
+    <t>Khuôn đục</t>
+  </si>
+  <si>
+    <t>Lớp số</t>
+  </si>
+  <si>
+    <t>Công đoạn</t>
+  </si>
+  <si>
+    <t>Nhóm công đoạn</t>
   </si>
 </sst>
 </file>
@@ -118,14 +130,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -407,44 +419,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="11" style="2" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="7" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="25.42578125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="10" style="3" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="17.85546875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="9.7109375" style="3" customWidth="1"/>
+    <col min="10" max="11" width="9.140625" style="3"/>
+    <col min="12" max="12" width="15.140625" style="3" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="3" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="2" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/kotlin/com/kcvn/spm/assets/template/ExportPlanTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ExportPlanTemplate.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Tỷ lệ đạt</t>
   </si>
@@ -55,6 +55,15 @@
   </si>
   <si>
     <t>Nhóm công đoạn</t>
+  </si>
+  <si>
+    <t>Tên rút gọn</t>
+  </si>
+  <si>
+    <t>Tên công đoạn</t>
+  </si>
+  <si>
+    <t>Lớp số của công đoạn phụ</t>
   </si>
 </sst>
 </file>
@@ -125,13 +134,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -419,58 +425,71 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.42578125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="9.5703125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="10" style="3" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="17.85546875" style="3" customWidth="1"/>
-    <col min="9" max="9" width="9.7109375" style="3" customWidth="1"/>
-    <col min="10" max="11" width="9.140625" style="3"/>
-    <col min="12" max="12" width="15.140625" style="3" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="3"/>
+    <col min="1" max="1" width="15.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="25.42578125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="10" style="2" customWidth="1"/>
+    <col min="6" max="6" width="11.5703125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="17" style="2" customWidth="1"/>
+    <col min="9" max="9" width="16.140625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="36.85546875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="15.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="9.7109375" style="2" customWidth="1"/>
+    <col min="13" max="13" width="10.28515625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" style="2" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" style="2" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="2" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>3</v>
       </c>
     </row>

--- a/src/main/kotlin/com/kcvn/spm/assets/template/ExportPlanTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ExportPlanTemplate.xlsx
@@ -442,7 +442,7 @@
     <col min="12" max="12" width="9.7109375" style="2" customWidth="1"/>
     <col min="13" max="13" width="10.28515625" style="2" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" style="2" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" style="2" customWidth="1"/>
+    <col min="15" max="15" width="16" style="2" customWidth="1"/>
     <col min="16" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>

--- a/src/main/kotlin/com/kcvn/spm/assets/template/ExportPlanTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ExportPlanTemplate.xlsx
@@ -19,15 +19,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Tỷ lệ đạt</t>
-  </si>
-  <si>
-    <t>Tồn</t>
-  </si>
-  <si>
-    <t>Tổng tồn</t>
   </si>
   <si>
     <t>日程</t>
@@ -425,7 +419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" style="2" customWidth="1"/>
@@ -440,57 +434,49 @@
     <col min="10" max="10" width="36.85546875" style="2" customWidth="1"/>
     <col min="11" max="11" width="15.28515625" style="2" customWidth="1"/>
     <col min="12" max="12" width="9.7109375" style="2" customWidth="1"/>
-    <col min="13" max="13" width="10.28515625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" style="2" customWidth="1"/>
-    <col min="15" max="15" width="16" style="2" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="2"/>
+    <col min="13" max="13" width="16" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>14</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/kotlin/com/kcvn/spm/assets/template/ExportPlanTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ExportPlanTemplate.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Tỷ lệ đạt</t>
   </si>
@@ -58,6 +58,9 @@
   </si>
   <si>
     <t>Lớp số của công đoạn phụ</t>
+  </si>
+  <si>
+    <t>Tổng</t>
   </si>
 </sst>
 </file>
@@ -419,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" style="2" customWidth="1"/>
@@ -435,10 +438,11 @@
     <col min="11" max="11" width="15.28515625" style="2" customWidth="1"/>
     <col min="12" max="12" width="9.7109375" style="2" customWidth="1"/>
     <col min="13" max="13" width="16" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="2"/>
+    <col min="14" max="14" width="13.140625" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -477,6 +481,9 @@
       </c>
       <c r="M1" s="1" t="s">
         <v>1</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/kotlin/com/kcvn/spm/assets/template/ExportPlanTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ExportPlanTemplate.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="Thông tin kế hoạch" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Thông tin kế hoạch'!$A$1:$M$1</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -30,12 +33,6 @@
     <t>Tên sản phẩm</t>
   </si>
   <si>
-    <t>Pcs/SH</t>
-  </si>
-  <si>
-    <t>Block/SH</t>
-  </si>
-  <si>
     <t>Line</t>
   </si>
   <si>
@@ -61,6 +58,12 @@
   </si>
   <si>
     <t>Tổng</t>
+  </si>
+  <si>
+    <t>Pcs/Block</t>
+  </si>
+  <si>
+    <t>Block</t>
   </si>
 </sst>
 </file>
@@ -427,7 +430,7 @@
   <cols>
     <col min="1" max="1" width="15.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="25.42578125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" style="2" customWidth="1"/>
     <col min="4" max="4" width="11.42578125" style="2" customWidth="1"/>
     <col min="5" max="5" width="10" style="2" customWidth="1"/>
     <col min="6" max="6" width="11.5703125" style="2" customWidth="1"/>
@@ -444,37 +447,37 @@
   <sheetData>
     <row r="1" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="K1" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>0</v>
@@ -483,10 +486,11 @@
         <v>1</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/src/main/kotlin/com/kcvn/spm/assets/template/ExportPlanTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ExportPlanTemplate.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Tỷ lệ đạt</t>
   </si>
@@ -57,13 +57,17 @@
     <t>Lớp số của công đoạn phụ</t>
   </si>
   <si>
-    <t>Tổng</t>
-  </si>
-  <si>
     <t>Pcs/Block</t>
   </si>
   <si>
     <t>Block</t>
+  </si>
+  <si>
+    <t>Tồn kho 
+chốt tồn</t>
+  </si>
+  <si>
+    <t>Tồn kho</t>
   </si>
 </sst>
 </file>
@@ -425,7 +429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" style="2" customWidth="1"/>
@@ -441,11 +445,12 @@
     <col min="11" max="11" width="15.28515625" style="2" customWidth="1"/>
     <col min="12" max="12" width="9.7109375" style="2" customWidth="1"/>
     <col min="13" max="13" width="16" style="2" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="2"/>
+    <col min="14" max="14" width="12.7109375" style="2" customWidth="1"/>
+    <col min="15" max="15" width="13.140625" style="2" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -453,10 +458,10 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -486,7 +491,10 @@
         <v>1</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
